--- a/public/import_luyen_noi/luyen noi Flyer.xlsx
+++ b/public/import_luyen_noi/luyen noi Flyer.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1163" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="429">
   <si>
     <t>STT</t>
   </si>
@@ -107,9 +107,6 @@
     <t>Tiếng Anh</t>
   </si>
   <si>
-    <t>Chủ đề|Loại câu trắc nghiệm|Đáp án đúng|Câu trắc nghiệm|Phương án 1|Phương án 2|Phương án 3|Phương án 4</t>
-  </si>
-  <si>
     <t>tenAnh</t>
   </si>
   <si>
@@ -1323,6 +1320,24 @@
   </si>
   <si>
     <t>Động vật yêu thích của tôi là cá heo. Chúng thân thiện, thông minh và có thể làm trò trong nước, thật tuyệt. Tôi hy vọng một ngày nào đó sẽ thấy chúng ngoài đời thật!</t>
+  </si>
+  <si>
+    <t>tách đáp án 1</t>
+  </si>
+  <si>
+    <t>tách đáp án 2</t>
+  </si>
+  <si>
+    <t>tách đáp án 3</t>
+  </si>
+  <si>
+    <t>đường dẫn ảnh 1</t>
+  </si>
+  <si>
+    <t>đường dẫn ảnh 2</t>
+  </si>
+  <si>
+    <t>đường dẫn ảnh 3</t>
   </si>
 </sst>
 </file>
@@ -1699,7 +1714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T691"/>
+  <dimension ref="A1:Y691"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="7" width="6.140625" customWidth="1"/>
@@ -1712,11 +1727,11 @@
     <col min="14" max="14" width="31.5703125" customWidth="1"/>
     <col min="19" max="19" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="19.85546875" customWidth="1"/>
-    <col min="21" max="21" width="37.140625" customWidth="1"/>
-    <col min="22" max="22" width="31.5703125" customWidth="1"/>
+    <col min="21" max="21" width="15.85546875" customWidth="1"/>
+    <col min="22" max="22" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="3" customFormat="1" ht="165">
+    <row r="1" spans="1:25" s="3" customFormat="1" ht="165">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1730,13 +1745,13 @@
         <v>8</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>13</v>
@@ -1760,7 +1775,7 @@
         <v>6</v>
       </c>
       <c r="O1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>9</v>
@@ -1774,488 +1789,503 @@
       <c r="S1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="T1" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20">
+      <c r="T1" t="s">
+        <v>423</v>
+      </c>
+      <c r="U1" t="s">
+        <v>424</v>
+      </c>
+      <c r="V1" t="s">
+        <v>425</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J2" t="s">
         <v>17</v>
       </c>
       <c r="K2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L2" t="s">
         <v>16</v>
       </c>
       <c r="M2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J3" t="s">
         <v>17</v>
       </c>
       <c r="K3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L3" t="s">
         <v>16</v>
       </c>
       <c r="M3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="N3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O3" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J4" t="s">
         <v>17</v>
       </c>
       <c r="K4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L4" t="s">
         <v>16</v>
       </c>
       <c r="M4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O4" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J5" t="s">
         <v>17</v>
       </c>
       <c r="K5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L5" t="s">
         <v>16</v>
       </c>
       <c r="M5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="G6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J6" t="s">
         <v>17</v>
       </c>
       <c r="K6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L6" t="s">
         <v>16</v>
       </c>
       <c r="M6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O6" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="G7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J7" t="s">
         <v>17</v>
       </c>
       <c r="K7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L7" t="s">
         <v>16</v>
       </c>
       <c r="M7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O7" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="G8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J8" t="s">
         <v>17</v>
       </c>
       <c r="K8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L8" t="s">
         <v>16</v>
       </c>
       <c r="M8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O8" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="G9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J9" t="s">
         <v>17</v>
       </c>
       <c r="K9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L9" t="s">
         <v>16</v>
       </c>
       <c r="M9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O9" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J10" t="s">
         <v>17</v>
       </c>
       <c r="K10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L10" t="s">
         <v>16</v>
       </c>
       <c r="M10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O10" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="G11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J11" t="s">
         <v>17</v>
       </c>
       <c r="K11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L11" t="s">
         <v>16</v>
       </c>
       <c r="M11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="N11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O11" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="G12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J12" t="s">
         <v>17</v>
       </c>
       <c r="K12" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L12" t="s">
         <v>16</v>
       </c>
       <c r="M12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="N12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O12" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13" t="s">
         <v>25</v>
       </c>
-      <c r="I13" t="s">
-        <v>25</v>
-      </c>
-      <c r="J13" t="s">
-        <v>17</v>
-      </c>
-      <c r="K13" t="s">
-        <v>26</v>
-      </c>
       <c r="L13" t="s">
         <v>16</v>
       </c>
       <c r="M13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="N13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O13" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H14" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14" t="s">
         <v>25</v>
       </c>
-      <c r="I14" t="s">
-        <v>25</v>
-      </c>
-      <c r="J14" t="s">
-        <v>17</v>
-      </c>
-      <c r="K14" t="s">
-        <v>26</v>
-      </c>
       <c r="L14" t="s">
         <v>16</v>
       </c>
       <c r="M14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O14" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K15" t="s">
         <v>25</v>
       </c>
-      <c r="I15" t="s">
-        <v>25</v>
-      </c>
-      <c r="J15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K15" t="s">
-        <v>26</v>
-      </c>
       <c r="L15" t="s">
         <v>16</v>
       </c>
       <c r="M15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O15" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H16" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" t="s">
+        <v>17</v>
+      </c>
+      <c r="K16" t="s">
         <v>25</v>
       </c>
-      <c r="I16" t="s">
-        <v>25</v>
-      </c>
-      <c r="J16" t="s">
-        <v>17</v>
-      </c>
-      <c r="K16" t="s">
-        <v>26</v>
-      </c>
       <c r="L16" t="s">
         <v>16</v>
       </c>
       <c r="M16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="N16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O16" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -2263,31 +2293,31 @@
         <v>16</v>
       </c>
       <c r="G17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17" t="s">
+        <v>17</v>
+      </c>
+      <c r="K17" t="s">
         <v>25</v>
       </c>
-      <c r="I17" t="s">
-        <v>25</v>
-      </c>
-      <c r="J17" t="s">
-        <v>17</v>
-      </c>
-      <c r="K17" t="s">
-        <v>26</v>
-      </c>
       <c r="L17" t="s">
         <v>16</v>
       </c>
       <c r="M17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O17" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:15">
@@ -2295,31 +2325,31 @@
         <v>17</v>
       </c>
       <c r="G18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" t="s">
+        <v>24</v>
+      </c>
+      <c r="J18" t="s">
+        <v>17</v>
+      </c>
+      <c r="K18" t="s">
         <v>25</v>
       </c>
-      <c r="I18" t="s">
-        <v>25</v>
-      </c>
-      <c r="J18" t="s">
-        <v>17</v>
-      </c>
-      <c r="K18" t="s">
-        <v>26</v>
-      </c>
       <c r="L18" t="s">
         <v>16</v>
       </c>
       <c r="M18" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O18" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="19" spans="1:15">
@@ -2327,31 +2357,31 @@
         <v>18</v>
       </c>
       <c r="G19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H19" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19" t="s">
+        <v>24</v>
+      </c>
+      <c r="J19" t="s">
+        <v>17</v>
+      </c>
+      <c r="K19" t="s">
         <v>25</v>
       </c>
-      <c r="I19" t="s">
-        <v>25</v>
-      </c>
-      <c r="J19" t="s">
-        <v>17</v>
-      </c>
-      <c r="K19" t="s">
-        <v>26</v>
-      </c>
       <c r="L19" t="s">
         <v>16</v>
       </c>
       <c r="M19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O19" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="20" spans="1:15">
@@ -2359,31 +2389,31 @@
         <v>19</v>
       </c>
       <c r="G20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H20" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" t="s">
+        <v>17</v>
+      </c>
+      <c r="K20" t="s">
         <v>25</v>
       </c>
-      <c r="I20" t="s">
-        <v>25</v>
-      </c>
-      <c r="J20" t="s">
-        <v>17</v>
-      </c>
-      <c r="K20" t="s">
-        <v>26</v>
-      </c>
       <c r="L20" t="s">
         <v>16</v>
       </c>
       <c r="M20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O20" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="21" spans="1:15">
@@ -2391,31 +2421,31 @@
         <v>20</v>
       </c>
       <c r="G21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" t="s">
+        <v>17</v>
+      </c>
+      <c r="K21" t="s">
         <v>25</v>
       </c>
-      <c r="I21" t="s">
-        <v>25</v>
-      </c>
-      <c r="J21" t="s">
-        <v>17</v>
-      </c>
-      <c r="K21" t="s">
-        <v>26</v>
-      </c>
       <c r="L21" t="s">
         <v>16</v>
       </c>
       <c r="M21" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="N21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O21" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -2423,31 +2453,31 @@
         <v>21</v>
       </c>
       <c r="G22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H22" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" t="s">
+        <v>17</v>
+      </c>
+      <c r="K22" t="s">
         <v>25</v>
       </c>
-      <c r="I22" t="s">
-        <v>25</v>
-      </c>
-      <c r="J22" t="s">
-        <v>17</v>
-      </c>
-      <c r="K22" t="s">
-        <v>26</v>
-      </c>
       <c r="L22" t="s">
         <v>16</v>
       </c>
       <c r="M22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="23" spans="1:15">
@@ -2455,31 +2485,31 @@
         <v>22</v>
       </c>
       <c r="G23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" t="s">
+        <v>17</v>
+      </c>
+      <c r="K23" t="s">
         <v>25</v>
       </c>
-      <c r="I23" t="s">
-        <v>25</v>
-      </c>
-      <c r="J23" t="s">
-        <v>17</v>
-      </c>
-      <c r="K23" t="s">
-        <v>26</v>
-      </c>
       <c r="L23" t="s">
         <v>16</v>
       </c>
       <c r="M23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O23" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="24" spans="1:15">
@@ -2487,31 +2517,31 @@
         <v>23</v>
       </c>
       <c r="G24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J24" t="s">
         <v>17</v>
       </c>
       <c r="K24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L24" t="s">
         <v>16</v>
       </c>
       <c r="M24" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="N24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O24" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="25" spans="1:15">
@@ -2519,31 +2549,31 @@
         <v>24</v>
       </c>
       <c r="G25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J25" t="s">
         <v>17</v>
       </c>
       <c r="K25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L25" t="s">
         <v>16</v>
       </c>
       <c r="M25" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="N25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O25" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="26" spans="1:15">
@@ -2551,31 +2581,31 @@
         <v>25</v>
       </c>
       <c r="G26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J26" t="s">
         <v>17</v>
       </c>
       <c r="K26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L26" t="s">
         <v>16</v>
       </c>
       <c r="M26" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="N26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O26" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="27" spans="1:15">
@@ -2583,31 +2613,31 @@
         <v>26</v>
       </c>
       <c r="G27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J27" t="s">
         <v>17</v>
       </c>
       <c r="K27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L27" t="s">
         <v>16</v>
       </c>
       <c r="M27" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N27" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O27" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="28" spans="1:15">
@@ -2615,31 +2645,31 @@
         <v>27</v>
       </c>
       <c r="G28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J28" t="s">
         <v>17</v>
       </c>
       <c r="K28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L28" t="s">
         <v>16</v>
       </c>
       <c r="M28" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="N28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O28" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="29" spans="1:15">
@@ -2647,31 +2677,31 @@
         <v>28</v>
       </c>
       <c r="G29" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J29" t="s">
         <v>17</v>
       </c>
       <c r="K29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L29" t="s">
         <v>16</v>
       </c>
       <c r="M29" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="30" spans="1:15">
@@ -2679,31 +2709,31 @@
         <v>29</v>
       </c>
       <c r="G30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J30" t="s">
         <v>17</v>
       </c>
       <c r="K30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L30" t="s">
         <v>16</v>
       </c>
       <c r="M30" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O30" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="31" spans="1:15">
@@ -2711,31 +2741,31 @@
         <v>30</v>
       </c>
       <c r="G31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J31" t="s">
         <v>17</v>
       </c>
       <c r="K31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L31" t="s">
         <v>16</v>
       </c>
       <c r="M31" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O31" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="32" spans="1:15">
@@ -2743,31 +2773,31 @@
         <v>31</v>
       </c>
       <c r="G32" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J32" t="s">
         <v>17</v>
       </c>
       <c r="K32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L32" t="s">
         <v>16</v>
       </c>
       <c r="M32" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N32" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O32" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="33" spans="1:15">
@@ -2775,31 +2805,31 @@
         <v>32</v>
       </c>
       <c r="G33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J33" t="s">
         <v>17</v>
       </c>
       <c r="K33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L33" t="s">
         <v>16</v>
       </c>
       <c r="M33" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N33" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O33" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="34" spans="1:15">
@@ -2807,31 +2837,31 @@
         <v>33</v>
       </c>
       <c r="G34" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H34" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I34" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J34" t="s">
         <v>17</v>
       </c>
       <c r="K34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L34" t="s">
         <v>16</v>
       </c>
       <c r="M34" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N34" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O34" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="35" spans="1:15">
@@ -2839,31 +2869,31 @@
         <v>34</v>
       </c>
       <c r="G35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J35" t="s">
         <v>17</v>
       </c>
       <c r="K35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L35" t="s">
         <v>16</v>
       </c>
       <c r="M35" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O35" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="36" spans="1:15">
@@ -2871,31 +2901,31 @@
         <v>35</v>
       </c>
       <c r="G36" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H36" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I36" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J36" t="s">
         <v>17</v>
       </c>
       <c r="K36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L36" t="s">
         <v>16</v>
       </c>
       <c r="M36" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O36" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="37" spans="1:15">
@@ -2903,31 +2933,31 @@
         <v>36</v>
       </c>
       <c r="G37" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J37" t="s">
         <v>17</v>
       </c>
       <c r="K37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L37" t="s">
         <v>16</v>
       </c>
       <c r="M37" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N37" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O37" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="38" spans="1:15">
@@ -2935,31 +2965,31 @@
         <v>37</v>
       </c>
       <c r="G38" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J38" t="s">
         <v>17</v>
       </c>
       <c r="K38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L38" t="s">
         <v>16</v>
       </c>
       <c r="M38" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N38" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O38" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="39" spans="1:15">
@@ -2967,31 +2997,31 @@
         <v>38</v>
       </c>
       <c r="G39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H39" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I39" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J39" t="s">
         <v>17</v>
       </c>
       <c r="K39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L39" t="s">
         <v>16</v>
       </c>
       <c r="M39" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N39" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O39" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="40" spans="1:15">
@@ -2999,31 +3029,31 @@
         <v>39</v>
       </c>
       <c r="G40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J40" t="s">
         <v>17</v>
       </c>
       <c r="K40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L40" t="s">
         <v>16</v>
       </c>
       <c r="M40" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O40" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="41" spans="1:15">
@@ -3031,31 +3061,31 @@
         <v>40</v>
       </c>
       <c r="G41" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H41" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I41" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J41" t="s">
         <v>17</v>
       </c>
       <c r="K41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L41" t="s">
         <v>16</v>
       </c>
       <c r="M41" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N41" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O41" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="42" spans="1:15">
@@ -3063,31 +3093,31 @@
         <v>41</v>
       </c>
       <c r="G42" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H42" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I42" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J42" t="s">
         <v>17</v>
       </c>
       <c r="K42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L42" t="s">
         <v>16</v>
       </c>
       <c r="M42" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="N42" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O42" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="43" spans="1:15">
@@ -3095,31 +3125,31 @@
         <v>42</v>
       </c>
       <c r="G43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H43" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I43" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J43" t="s">
         <v>17</v>
       </c>
       <c r="K43" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L43" t="s">
         <v>16</v>
       </c>
       <c r="M43" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N43" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O43" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="44" spans="1:15">
@@ -3127,31 +3157,31 @@
         <v>43</v>
       </c>
       <c r="G44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H44" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I44" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J44" t="s">
         <v>17</v>
       </c>
       <c r="K44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L44" t="s">
         <v>16</v>
       </c>
       <c r="M44" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="N44" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O44" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="45" spans="1:15">
@@ -3159,31 +3189,31 @@
         <v>44</v>
       </c>
       <c r="G45" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H45" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I45" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J45" t="s">
         <v>17</v>
       </c>
       <c r="K45" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L45" t="s">
         <v>16</v>
       </c>
       <c r="M45" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="N45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O45" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="46" spans="1:15">
@@ -3191,31 +3221,31 @@
         <v>45</v>
       </c>
       <c r="G46" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H46" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I46" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J46" t="s">
         <v>17</v>
       </c>
       <c r="K46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L46" t="s">
         <v>16</v>
       </c>
       <c r="M46" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N46" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O46" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="47" spans="1:15">
@@ -3223,31 +3253,31 @@
         <v>46</v>
       </c>
       <c r="G47" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H47" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I47" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J47" t="s">
         <v>17</v>
       </c>
       <c r="K47" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L47" t="s">
         <v>16</v>
       </c>
       <c r="M47" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N47" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O47" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="48" spans="1:15">
@@ -3255,31 +3285,31 @@
         <v>47</v>
       </c>
       <c r="G48" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J48" t="s">
         <v>17</v>
       </c>
       <c r="K48" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L48" t="s">
         <v>16</v>
       </c>
       <c r="M48" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="N48" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O48" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="49" spans="1:15">
@@ -3287,31 +3317,31 @@
         <v>48</v>
       </c>
       <c r="G49" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J49" t="s">
         <v>17</v>
       </c>
       <c r="K49" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L49" t="s">
         <v>16</v>
       </c>
       <c r="M49" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O49" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="50" spans="1:15">
@@ -3319,31 +3349,31 @@
         <v>49</v>
       </c>
       <c r="G50" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H50" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I50" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J50" t="s">
         <v>17</v>
       </c>
       <c r="K50" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L50" t="s">
         <v>16</v>
       </c>
       <c r="M50" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="N50" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O50" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="51" spans="1:15">
@@ -3351,31 +3381,31 @@
         <v>50</v>
       </c>
       <c r="G51" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H51" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I51" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J51" t="s">
         <v>17</v>
       </c>
       <c r="K51" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L51" t="s">
         <v>16</v>
       </c>
       <c r="M51" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N51" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O51" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="52" spans="1:15">
@@ -3383,31 +3413,31 @@
         <v>51</v>
       </c>
       <c r="G52" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H52" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I52" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J52" t="s">
         <v>17</v>
       </c>
       <c r="K52" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L52" t="s">
         <v>16</v>
       </c>
       <c r="M52" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N52" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O52" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="53" spans="1:15">
@@ -3415,31 +3445,31 @@
         <v>52</v>
       </c>
       <c r="G53" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J53" t="s">
         <v>17</v>
       </c>
       <c r="K53" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L53" t="s">
         <v>16</v>
       </c>
       <c r="M53" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="N53" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O53" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="54" spans="1:15">
@@ -3447,31 +3477,31 @@
         <v>53</v>
       </c>
       <c r="G54" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H54" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I54" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J54" t="s">
         <v>17</v>
       </c>
       <c r="K54" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L54" t="s">
         <v>16</v>
       </c>
       <c r="M54" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N54" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O54" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="55" spans="1:15">
@@ -3479,31 +3509,31 @@
         <v>54</v>
       </c>
       <c r="G55" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H55" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I55" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J55" t="s">
         <v>17</v>
       </c>
       <c r="K55" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L55" t="s">
         <v>16</v>
       </c>
       <c r="M55" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="N55" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O55" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="56" spans="1:15">
@@ -3511,31 +3541,31 @@
         <v>55</v>
       </c>
       <c r="G56" t="s">
+        <v>20</v>
+      </c>
+      <c r="H56" t="s">
+        <v>24</v>
+      </c>
+      <c r="I56" t="s">
+        <v>24</v>
+      </c>
+      <c r="J56" t="s">
+        <v>17</v>
+      </c>
+      <c r="K56" t="s">
+        <v>30</v>
+      </c>
+      <c r="L56" t="s">
+        <v>16</v>
+      </c>
+      <c r="M56" t="s">
+        <v>215</v>
+      </c>
+      <c r="N56" t="s">
         <v>21</v>
       </c>
-      <c r="H56" t="s">
-        <v>25</v>
-      </c>
-      <c r="I56" t="s">
-        <v>25</v>
-      </c>
-      <c r="J56" t="s">
-        <v>17</v>
-      </c>
-      <c r="K56" t="s">
-        <v>31</v>
-      </c>
-      <c r="L56" t="s">
-        <v>16</v>
-      </c>
-      <c r="M56" t="s">
-        <v>216</v>
-      </c>
-      <c r="N56" t="s">
-        <v>22</v>
-      </c>
       <c r="O56" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="57" spans="1:15">
@@ -3543,31 +3573,31 @@
         <v>56</v>
       </c>
       <c r="G57" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H57" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I57" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J57" t="s">
         <v>17</v>
       </c>
       <c r="K57" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L57" t="s">
         <v>16</v>
       </c>
       <c r="M57" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N57" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O57" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="58" spans="1:15">
@@ -3575,31 +3605,31 @@
         <v>57</v>
       </c>
       <c r="G58" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H58" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I58" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J58" t="s">
         <v>17</v>
       </c>
       <c r="K58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L58" t="s">
         <v>16</v>
       </c>
       <c r="M58" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N58" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O58" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="59" spans="1:15">
@@ -3607,31 +3637,31 @@
         <v>58</v>
       </c>
       <c r="G59" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H59" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I59" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J59" t="s">
         <v>17</v>
       </c>
       <c r="K59" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L59" t="s">
         <v>16</v>
       </c>
       <c r="M59" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N59" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O59" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="60" spans="1:15">
@@ -3639,31 +3669,31 @@
         <v>59</v>
       </c>
       <c r="G60" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H60" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I60" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J60" t="s">
         <v>17</v>
       </c>
       <c r="K60" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L60" t="s">
         <v>16</v>
       </c>
       <c r="M60" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N60" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O60" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="61" spans="1:15">
@@ -3671,31 +3701,31 @@
         <v>60</v>
       </c>
       <c r="G61" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H61" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I61" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J61" t="s">
         <v>17</v>
       </c>
       <c r="K61" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L61" t="s">
         <v>16</v>
       </c>
       <c r="M61" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="N61" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O61" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="62" spans="1:15">
@@ -3703,31 +3733,31 @@
         <v>61</v>
       </c>
       <c r="G62" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H62" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I62" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J62" t="s">
         <v>17</v>
       </c>
       <c r="K62" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L62" t="s">
         <v>16</v>
       </c>
       <c r="M62" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="N62" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O62" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="63" spans="1:15">
@@ -3735,31 +3765,31 @@
         <v>62</v>
       </c>
       <c r="G63" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H63" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I63" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J63" t="s">
         <v>17</v>
       </c>
       <c r="K63" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L63" t="s">
         <v>16</v>
       </c>
       <c r="M63" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N63" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O63" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="64" spans="1:15">
@@ -3767,31 +3797,31 @@
         <v>63</v>
       </c>
       <c r="G64" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H64" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I64" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J64" t="s">
         <v>17</v>
       </c>
       <c r="K64" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L64" t="s">
         <v>16</v>
       </c>
       <c r="M64" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="N64" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O64" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="65" spans="1:15">
@@ -3799,31 +3829,31 @@
         <v>64</v>
       </c>
       <c r="G65" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H65" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I65" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J65" t="s">
         <v>17</v>
       </c>
       <c r="K65" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L65" t="s">
         <v>16</v>
       </c>
       <c r="M65" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O65" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="66" spans="1:15">
@@ -3831,31 +3861,31 @@
         <v>65</v>
       </c>
       <c r="G66" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H66" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I66" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J66" t="s">
         <v>17</v>
       </c>
       <c r="K66" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L66" t="s">
         <v>16</v>
       </c>
       <c r="M66" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="N66" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O66" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="67" spans="1:15">
@@ -3863,31 +3893,31 @@
         <v>66</v>
       </c>
       <c r="G67" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H67" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I67" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J67" t="s">
         <v>17</v>
       </c>
       <c r="K67" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L67" t="s">
         <v>16</v>
       </c>
       <c r="M67" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N67" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O67" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="68" spans="1:15">
@@ -3895,31 +3925,31 @@
         <v>67</v>
       </c>
       <c r="G68" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H68" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I68" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J68" t="s">
         <v>17</v>
       </c>
       <c r="K68" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L68" t="s">
         <v>16</v>
       </c>
       <c r="M68" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="N68" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O68" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="69" spans="1:15">
@@ -3927,31 +3957,31 @@
         <v>68</v>
       </c>
       <c r="G69" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H69" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I69" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J69" t="s">
         <v>17</v>
       </c>
       <c r="K69" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L69" t="s">
         <v>16</v>
       </c>
       <c r="M69" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="N69" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O69" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="70" spans="1:15">
@@ -3959,31 +3989,31 @@
         <v>69</v>
       </c>
       <c r="G70" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H70" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I70" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J70" t="s">
         <v>17</v>
       </c>
       <c r="K70" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L70" t="s">
         <v>16</v>
       </c>
       <c r="M70" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="N70" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O70" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="71" spans="1:15">
@@ -3991,31 +4021,31 @@
         <v>70</v>
       </c>
       <c r="G71" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H71" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I71" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J71" t="s">
         <v>17</v>
       </c>
       <c r="K71" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L71" t="s">
         <v>16</v>
       </c>
       <c r="M71" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="N71" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O71" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="72" spans="1:15">
@@ -4023,31 +4053,31 @@
         <v>71</v>
       </c>
       <c r="G72" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H72" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I72" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J72" t="s">
         <v>17</v>
       </c>
       <c r="K72" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L72" t="s">
         <v>16</v>
       </c>
       <c r="M72" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N72" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O72" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="73" spans="1:15">
@@ -4055,31 +4085,31 @@
         <v>72</v>
       </c>
       <c r="G73" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H73" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I73" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J73" t="s">
         <v>17</v>
       </c>
       <c r="K73" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L73" t="s">
         <v>16</v>
       </c>
       <c r="M73" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N73" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O73" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="74" spans="1:15">
@@ -4087,31 +4117,31 @@
         <v>73</v>
       </c>
       <c r="G74" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H74" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I74" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J74" t="s">
         <v>17</v>
       </c>
       <c r="K74" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L74" t="s">
         <v>16</v>
       </c>
       <c r="M74" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N74" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O74" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="75" spans="1:15">
@@ -4119,31 +4149,31 @@
         <v>74</v>
       </c>
       <c r="G75" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H75" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I75" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J75" t="s">
         <v>17</v>
       </c>
       <c r="K75" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L75" t="s">
         <v>16</v>
       </c>
       <c r="M75" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N75" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O75" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="76" spans="1:15">
@@ -4151,31 +4181,31 @@
         <v>75</v>
       </c>
       <c r="G76" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H76" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I76" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J76" t="s">
         <v>17</v>
       </c>
       <c r="K76" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L76" t="s">
         <v>16</v>
       </c>
       <c r="M76" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="N76" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O76" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="77" spans="1:15">
@@ -4183,31 +4213,31 @@
         <v>76</v>
       </c>
       <c r="G77" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H77" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I77" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J77" t="s">
         <v>17</v>
       </c>
       <c r="K77" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L77" t="s">
         <v>16</v>
       </c>
       <c r="M77" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="N77" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O77" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="78" spans="1:15">
@@ -4215,31 +4245,31 @@
         <v>77</v>
       </c>
       <c r="G78" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H78" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I78" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J78" t="s">
         <v>17</v>
       </c>
       <c r="K78" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L78" t="s">
         <v>16</v>
       </c>
       <c r="M78" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N78" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O78" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="79" spans="1:15">
@@ -4247,31 +4277,31 @@
         <v>78</v>
       </c>
       <c r="G79" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H79" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I79" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J79" t="s">
         <v>17</v>
       </c>
       <c r="K79" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L79" t="s">
         <v>16</v>
       </c>
       <c r="M79" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="N79" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O79" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="80" spans="1:15">
@@ -4279,31 +4309,31 @@
         <v>79</v>
       </c>
       <c r="G80" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H80" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I80" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J80" t="s">
         <v>17</v>
       </c>
       <c r="K80" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L80" t="s">
         <v>16</v>
       </c>
       <c r="M80" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="N80" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O80" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="81" spans="1:15">
@@ -4311,31 +4341,31 @@
         <v>80</v>
       </c>
       <c r="G81" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H81" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I81" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J81" t="s">
         <v>17</v>
       </c>
       <c r="K81" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L81" t="s">
         <v>16</v>
       </c>
       <c r="M81" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="N81" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O81" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="82" spans="1:15">
@@ -4343,31 +4373,31 @@
         <v>81</v>
       </c>
       <c r="G82" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H82" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I82" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J82" t="s">
         <v>17</v>
       </c>
       <c r="K82" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L82" t="s">
         <v>16</v>
       </c>
       <c r="M82" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="N82" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O82" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="83" spans="1:15">
@@ -4375,31 +4405,31 @@
         <v>82</v>
       </c>
       <c r="G83" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H83" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I83" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J83" t="s">
         <v>17</v>
       </c>
       <c r="K83" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L83" t="s">
         <v>16</v>
       </c>
       <c r="M83" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="N83" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O83" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="84" spans="1:15">
@@ -4407,31 +4437,31 @@
         <v>83</v>
       </c>
       <c r="G84" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H84" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I84" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J84" t="s">
         <v>17</v>
       </c>
       <c r="K84" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L84" t="s">
         <v>16</v>
       </c>
       <c r="M84" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N84" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O84" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="85" spans="1:15">
@@ -4439,31 +4469,31 @@
         <v>84</v>
       </c>
       <c r="G85" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H85" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I85" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J85" t="s">
         <v>17</v>
       </c>
       <c r="K85" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L85" t="s">
         <v>16</v>
       </c>
       <c r="M85" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="N85" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O85" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="86" spans="1:15">
@@ -4471,31 +4501,31 @@
         <v>85</v>
       </c>
       <c r="G86" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H86" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I86" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J86" t="s">
         <v>17</v>
       </c>
       <c r="K86" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L86" t="s">
         <v>16</v>
       </c>
       <c r="M86" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="N86" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O86" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="87" spans="1:15">
@@ -4503,31 +4533,31 @@
         <v>86</v>
       </c>
       <c r="G87" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H87" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I87" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J87" t="s">
         <v>17</v>
       </c>
       <c r="K87" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L87" t="s">
         <v>16</v>
       </c>
       <c r="M87" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="N87" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O87" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="88" spans="1:15">
@@ -4535,31 +4565,31 @@
         <v>87</v>
       </c>
       <c r="G88" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H88" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I88" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J88" t="s">
         <v>17</v>
       </c>
       <c r="K88" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L88" t="s">
         <v>16</v>
       </c>
       <c r="M88" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="N88" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O88" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="89" spans="1:15">
@@ -4567,31 +4597,31 @@
         <v>88</v>
       </c>
       <c r="G89" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H89" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I89" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J89" t="s">
         <v>17</v>
       </c>
       <c r="K89" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L89" t="s">
         <v>16</v>
       </c>
       <c r="M89" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="N89" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O89" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="90" spans="1:15">
@@ -4599,31 +4629,31 @@
         <v>89</v>
       </c>
       <c r="G90" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H90" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I90" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J90" t="s">
         <v>17</v>
       </c>
       <c r="K90" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L90" t="s">
         <v>16</v>
       </c>
       <c r="M90" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="N90" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O90" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="91" spans="1:15">
@@ -4631,31 +4661,31 @@
         <v>90</v>
       </c>
       <c r="G91" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H91" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I91" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J91" t="s">
         <v>17</v>
       </c>
       <c r="K91" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L91" t="s">
         <v>16</v>
       </c>
       <c r="M91" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N91" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O91" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="92" spans="1:15">
@@ -4663,31 +4693,31 @@
         <v>91</v>
       </c>
       <c r="G92" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H92" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I92" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J92" t="s">
         <v>17</v>
       </c>
       <c r="K92" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L92" t="s">
         <v>16</v>
       </c>
       <c r="M92" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N92" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O92" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="93" spans="1:15">
@@ -4695,31 +4725,31 @@
         <v>92</v>
       </c>
       <c r="G93" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H93" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I93" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J93" t="s">
         <v>17</v>
       </c>
       <c r="K93" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L93" t="s">
         <v>16</v>
       </c>
       <c r="M93" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="N93" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O93" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="94" spans="1:15">
@@ -4727,31 +4757,31 @@
         <v>93</v>
       </c>
       <c r="G94" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H94" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I94" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J94" t="s">
         <v>17</v>
       </c>
       <c r="K94" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L94" t="s">
         <v>16</v>
       </c>
       <c r="M94" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N94" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O94" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="95" spans="1:15">
@@ -4759,31 +4789,31 @@
         <v>94</v>
       </c>
       <c r="G95" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H95" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I95" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J95" t="s">
         <v>17</v>
       </c>
       <c r="K95" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L95" t="s">
         <v>16</v>
       </c>
       <c r="M95" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="N95" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O95" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="96" spans="1:15">
@@ -4791,31 +4821,31 @@
         <v>95</v>
       </c>
       <c r="G96" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H96" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I96" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J96" t="s">
         <v>17</v>
       </c>
       <c r="K96" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L96" t="s">
         <v>16</v>
       </c>
       <c r="M96" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="N96" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O96" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="97" spans="1:15">
@@ -4823,31 +4853,31 @@
         <v>96</v>
       </c>
       <c r="G97" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H97" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I97" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J97" t="s">
         <v>17</v>
       </c>
       <c r="K97" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L97" t="s">
         <v>16</v>
       </c>
       <c r="M97" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="N97" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O97" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="98" spans="1:15">
@@ -4855,31 +4885,31 @@
         <v>97</v>
       </c>
       <c r="G98" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H98" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I98" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J98" t="s">
         <v>17</v>
       </c>
       <c r="K98" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L98" t="s">
         <v>16</v>
       </c>
       <c r="M98" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N98" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O98" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="99" spans="1:15">
@@ -4887,31 +4917,31 @@
         <v>98</v>
       </c>
       <c r="G99" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H99" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I99" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J99" t="s">
         <v>17</v>
       </c>
       <c r="K99" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L99" t="s">
         <v>16</v>
       </c>
       <c r="M99" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N99" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O99" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="100" spans="1:15">
@@ -4919,31 +4949,31 @@
         <v>99</v>
       </c>
       <c r="G100" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H100" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I100" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J100" t="s">
         <v>17</v>
       </c>
       <c r="K100" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L100" t="s">
         <v>16</v>
       </c>
       <c r="M100" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="N100" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O100" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="101" spans="1:15">
@@ -4951,31 +4981,31 @@
         <v>100</v>
       </c>
       <c r="G101" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H101" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I101" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J101" t="s">
         <v>17</v>
       </c>
       <c r="K101" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L101" t="s">
         <v>16</v>
       </c>
       <c r="M101" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N101" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O101" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="102" spans="1:15">
@@ -4983,31 +5013,31 @@
         <v>101</v>
       </c>
       <c r="G102" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H102" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I102" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J102" t="s">
         <v>17</v>
       </c>
       <c r="K102" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L102" t="s">
         <v>16</v>
       </c>
       <c r="M102" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N102" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O102" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="103" spans="1:15">
@@ -5015,31 +5045,31 @@
         <v>102</v>
       </c>
       <c r="G103" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H103" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I103" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J103" t="s">
         <v>17</v>
       </c>
       <c r="K103" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L103" t="s">
         <v>16</v>
       </c>
       <c r="M103" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N103" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O103" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="104" spans="1:15">
@@ -5047,31 +5077,31 @@
         <v>103</v>
       </c>
       <c r="G104" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H104" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I104" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J104" t="s">
         <v>17</v>
       </c>
       <c r="K104" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L104" t="s">
         <v>16</v>
       </c>
       <c r="M104" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="N104" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O104" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="105" spans="1:15">
@@ -5079,31 +5109,31 @@
         <v>104</v>
       </c>
       <c r="G105" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H105" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I105" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J105" t="s">
         <v>17</v>
       </c>
       <c r="K105" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L105" t="s">
         <v>16</v>
       </c>
       <c r="M105" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N105" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O105" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="106" spans="1:15">
@@ -5111,31 +5141,31 @@
         <v>105</v>
       </c>
       <c r="G106" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H106" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I106" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J106" t="s">
         <v>17</v>
       </c>
       <c r="K106" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L106" t="s">
         <v>16</v>
       </c>
       <c r="M106" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N106" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O106" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="107" spans="1:15">
@@ -5143,31 +5173,31 @@
         <v>106</v>
       </c>
       <c r="G107" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H107" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I107" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J107" t="s">
         <v>17</v>
       </c>
       <c r="K107" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L107" t="s">
         <v>16</v>
       </c>
       <c r="M107" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N107" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O107" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="108" spans="1:15">
@@ -5175,31 +5205,31 @@
         <v>107</v>
       </c>
       <c r="G108" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H108" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I108" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J108" t="s">
         <v>17</v>
       </c>
       <c r="K108" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L108" t="s">
         <v>16</v>
       </c>
       <c r="M108" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="N108" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O108" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="109" spans="1:15">
@@ -5207,31 +5237,31 @@
         <v>108</v>
       </c>
       <c r="G109" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H109" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I109" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J109" t="s">
         <v>17</v>
       </c>
       <c r="K109" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L109" t="s">
         <v>16</v>
       </c>
       <c r="M109" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N109" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O109" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="110" spans="1:15">
@@ -5239,31 +5269,31 @@
         <v>109</v>
       </c>
       <c r="G110" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H110" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I110" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J110" t="s">
         <v>17</v>
       </c>
       <c r="K110" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L110" t="s">
         <v>16</v>
       </c>
       <c r="M110" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="N110" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O110" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="111" spans="1:15">
@@ -5271,31 +5301,31 @@
         <v>110</v>
       </c>
       <c r="G111" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H111" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I111" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J111" t="s">
         <v>17</v>
       </c>
       <c r="K111" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L111" t="s">
         <v>16</v>
       </c>
       <c r="M111" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="N111" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O111" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="112" spans="1:15">
@@ -5303,31 +5333,31 @@
         <v>111</v>
       </c>
       <c r="G112" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H112" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I112" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J112" t="s">
         <v>17</v>
       </c>
       <c r="K112" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L112" t="s">
         <v>16</v>
       </c>
       <c r="M112" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N112" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O112" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="113" spans="1:15">
@@ -5335,31 +5365,31 @@
         <v>112</v>
       </c>
       <c r="G113" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H113" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I113" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J113" t="s">
         <v>17</v>
       </c>
       <c r="K113" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L113" t="s">
         <v>16</v>
       </c>
       <c r="M113" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="N113" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O113" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="114" spans="1:15">
@@ -5367,31 +5397,31 @@
         <v>113</v>
       </c>
       <c r="G114" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H114" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I114" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J114" t="s">
         <v>17</v>
       </c>
       <c r="K114" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L114" t="s">
         <v>16</v>
       </c>
       <c r="M114" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="N114" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O114" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="115" spans="1:15">
@@ -5399,31 +5429,31 @@
         <v>114</v>
       </c>
       <c r="G115" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H115" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I115" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J115" t="s">
         <v>17</v>
       </c>
       <c r="K115" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L115" t="s">
         <v>16</v>
       </c>
       <c r="M115" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N115" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O115" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="116" spans="1:15">
@@ -5431,31 +5461,31 @@
         <v>115</v>
       </c>
       <c r="G116" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H116" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I116" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J116" t="s">
         <v>17</v>
       </c>
       <c r="K116" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L116" t="s">
         <v>16</v>
       </c>
       <c r="M116" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="N116" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O116" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="117" spans="1:15">
@@ -5463,31 +5493,31 @@
         <v>116</v>
       </c>
       <c r="G117" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H117" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I117" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J117" t="s">
         <v>17</v>
       </c>
       <c r="K117" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L117" t="s">
         <v>16</v>
       </c>
       <c r="M117" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="N117" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O117" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="118" spans="1:15">
@@ -5495,31 +5525,31 @@
         <v>117</v>
       </c>
       <c r="G118" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H118" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I118" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J118" t="s">
         <v>17</v>
       </c>
       <c r="K118" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L118" t="s">
         <v>16</v>
       </c>
       <c r="M118" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="N118" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O118" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="119" spans="1:15">
@@ -5527,31 +5557,31 @@
         <v>118</v>
       </c>
       <c r="G119" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H119" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I119" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J119" t="s">
         <v>17</v>
       </c>
       <c r="K119" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L119" t="s">
         <v>16</v>
       </c>
       <c r="M119" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N119" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O119" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="120" spans="1:15">
@@ -5559,31 +5589,31 @@
         <v>119</v>
       </c>
       <c r="G120" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H120" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I120" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J120" t="s">
         <v>17</v>
       </c>
       <c r="K120" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L120" t="s">
         <v>16</v>
       </c>
       <c r="M120" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N120" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O120" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="121" spans="1:15">
@@ -5591,31 +5621,31 @@
         <v>120</v>
       </c>
       <c r="G121" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H121" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I121" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J121" t="s">
         <v>17</v>
       </c>
       <c r="K121" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L121" t="s">
         <v>16</v>
       </c>
       <c r="M121" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N121" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O121" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="122" spans="1:15">
@@ -5623,31 +5653,31 @@
         <v>121</v>
       </c>
       <c r="G122" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H122" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I122" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J122" t="s">
         <v>17</v>
       </c>
       <c r="K122" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L122" t="s">
         <v>16</v>
       </c>
       <c r="M122" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N122" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O122" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="123" spans="1:15">
@@ -5655,31 +5685,31 @@
         <v>122</v>
       </c>
       <c r="G123" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H123" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I123" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J123" t="s">
         <v>17</v>
       </c>
       <c r="K123" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L123" t="s">
         <v>16</v>
       </c>
       <c r="M123" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N123" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O123" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="124" spans="1:15">
@@ -5687,31 +5717,31 @@
         <v>123</v>
       </c>
       <c r="G124" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H124" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I124" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J124" t="s">
         <v>17</v>
       </c>
       <c r="K124" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L124" t="s">
         <v>16</v>
       </c>
       <c r="M124" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N124" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O124" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="125" spans="1:15">
@@ -5719,31 +5749,31 @@
         <v>124</v>
       </c>
       <c r="G125" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H125" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I125" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J125" t="s">
         <v>17</v>
       </c>
       <c r="K125" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L125" t="s">
         <v>16</v>
       </c>
       <c r="M125" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="N125" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O125" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="126" spans="1:15">
@@ -5751,31 +5781,31 @@
         <v>125</v>
       </c>
       <c r="G126" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H126" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I126" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J126" t="s">
         <v>17</v>
       </c>
       <c r="K126" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L126" t="s">
         <v>16</v>
       </c>
       <c r="M126" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="N126" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O126" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="127" spans="1:15">
@@ -5783,31 +5813,31 @@
         <v>126</v>
       </c>
       <c r="G127" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H127" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I127" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J127" t="s">
         <v>17</v>
       </c>
       <c r="K127" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L127" t="s">
         <v>16</v>
       </c>
       <c r="M127" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N127" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O127" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="128" spans="1:15">
@@ -5815,31 +5845,31 @@
         <v>127</v>
       </c>
       <c r="G128" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H128" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I128" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J128" t="s">
         <v>17</v>
       </c>
       <c r="K128" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L128" t="s">
         <v>16</v>
       </c>
       <c r="M128" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N128" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O128" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="129" spans="1:11">
